--- a/artfynd/A 40177-2026 artfynd.xlsx
+++ b/artfynd/A 40177-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137522894</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137522829</v>
       </c>
       <c r="B3" t="n">
-        <v>96660</v>
+        <v>96663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,27 +884,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137523002</v>
+        <v>137548465</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,18 +917,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lohallen, Ryssberget, Norra, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473159</v>
+        <v>473171</v>
       </c>
       <c r="R4" t="n">
-        <v>6229115</v>
+        <v>6229006</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -960,7 +958,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +968,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,6 +993,124 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137548465</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137523002</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58197</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lohallen, Ryssberget, Norra, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>473159</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6229115</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bromölla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näsum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137523002</t>
         </is>
@@ -1005,6 +1121,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
